--- a/養蟲組.xlsx
+++ b/養蟲組.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmbdcrc\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\藥效測試\practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0827E20A-ED6A-40BD-8E4C-D19CC96B9ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D911BF-498D-4693-8538-CF9BD7A13889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9780DB9A-7D52-4A84-923D-98EB015C6B50}"/>
   </bookViews>

--- a/養蟲組.xlsx
+++ b/養蟲組.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\藥效測試\practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D911BF-498D-4693-8538-CF9BD7A13889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063B4BAB-CCD1-4995-A259-B63C743A07FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9780DB9A-7D52-4A84-923D-98EB015C6B50}"/>
   </bookViews>
@@ -263,10 +263,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>實驗方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>水噴</t>
   </si>
   <si>
@@ -311,6 +307,10 @@
   </si>
   <si>
     <t>9/9</t>
+  </si>
+  <si>
+    <t>實驗方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -688,7 +688,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -712,7 +712,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -720,7 +720,7 @@
         <v>2020</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -746,7 +746,7 @@
         <v>2020</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -772,7 +772,7 @@
         <v>2020</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -798,7 +798,7 @@
         <v>2020</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -824,7 +824,7 @@
         <v>2020</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -850,7 +850,7 @@
         <v>2020</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
@@ -868,7 +868,7 @@
         <v>2019</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -876,7 +876,7 @@
         <v>2020</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
@@ -894,7 +894,7 @@
         <v>2019</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
         <v>2020</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
@@ -920,7 +920,7 @@
         <v>2019</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -928,7 +928,7 @@
         <v>2020</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>7</v>
@@ -946,7 +946,7 @@
         <v>2019</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -954,7 +954,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>7</v>
@@ -972,7 +972,7 @@
         <v>2019</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1006,7 +1006,7 @@
         <v>2020</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>6</v>
@@ -1024,7 +1024,7 @@
         <v>2019</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1032,7 +1032,7 @@
         <v>2020</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
@@ -1050,7 +1050,7 @@
         <v>2019</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1058,7 +1058,7 @@
         <v>2020</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
@@ -1076,7 +1076,7 @@
         <v>2019</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1084,7 +1084,7 @@
         <v>2020</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
@@ -1102,7 +1102,7 @@
         <v>2019</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1110,7 +1110,7 @@
         <v>2020</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>6</v>
@@ -1128,7 +1128,7 @@
         <v>2019</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1136,7 +1136,7 @@
         <v>2020</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>10</v>
@@ -1151,7 +1151,7 @@
         <v>71</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1159,7 +1159,7 @@
         <v>2020</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>10</v>
@@ -1177,7 +1177,7 @@
         <v>2019</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1185,7 +1185,7 @@
         <v>2020</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
@@ -1203,7 +1203,7 @@
         <v>2019</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1211,7 +1211,7 @@
         <v>2020</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>10</v>
@@ -1229,7 +1229,7 @@
         <v>2019</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1237,7 +1237,7 @@
         <v>2020</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
@@ -1255,7 +1255,7 @@
         <v>2019</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1263,7 +1263,7 @@
         <v>2020</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>10</v>
@@ -1281,7 +1281,7 @@
         <v>2019</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1289,7 +1289,7 @@
         <v>2020</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
@@ -1307,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1315,7 +1315,7 @@
         <v>2020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>10</v>
@@ -1333,7 +1333,7 @@
         <v>2019</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1341,7 +1341,7 @@
         <v>2020</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
@@ -1359,7 +1359,7 @@
         <v>2019</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1367,7 +1367,7 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>6</v>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1393,7 +1393,7 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>6</v>
@@ -1411,7 +1411,7 @@
         <v>2019</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1419,7 +1419,7 @@
         <v>2020</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>6</v>
@@ -1437,7 +1437,7 @@
         <v>2019</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1445,7 +1445,7 @@
         <v>2020</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>7</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1471,7 +1471,7 @@
         <v>2020</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>7</v>
@@ -1489,7 +1489,7 @@
         <v>2019</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1497,7 +1497,7 @@
         <v>2020</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>7</v>
@@ -1515,7 +1515,7 @@
         <v>2019</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1523,7 +1523,7 @@
         <v>2020</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>11</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1549,7 +1549,7 @@
         <v>2020</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>11</v>
@@ -1567,7 +1567,7 @@
         <v>2019</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -1575,7 +1575,7 @@
         <v>2020</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>11</v>
@@ -1593,7 +1593,7 @@
         <v>2019</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1601,7 +1601,7 @@
         <v>2020</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>11</v>
@@ -1619,7 +1619,7 @@
         <v>2019</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -1627,7 +1627,7 @@
         <v>2020</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>11</v>
@@ -1645,7 +1645,7 @@
         <v>2019</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -1653,7 +1653,7 @@
         <v>2020</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>11</v>
@@ -1671,7 +1671,7 @@
         <v>2019</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -1679,7 +1679,7 @@
         <v>2020</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>11</v>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -1705,7 +1705,7 @@
         <v>2020</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>11</v>
@@ -1723,7 +1723,7 @@
         <v>2019</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -1731,7 +1731,7 @@
         <v>2020</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>11</v>
@@ -1749,7 +1749,7 @@
         <v>2019</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -1757,7 +1757,7 @@
         <v>2020</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>11</v>
@@ -1775,7 +1775,7 @@
         <v>2019</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -1783,7 +1783,7 @@
         <v>2020</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>12</v>
@@ -1801,7 +1801,7 @@
         <v>2019</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -1809,7 +1809,7 @@
         <v>2020</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>12</v>
@@ -1827,7 +1827,7 @@
         <v>2019</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -1835,7 +1835,7 @@
         <v>2020</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>12</v>
@@ -1853,7 +1853,7 @@
         <v>2019</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -1861,7 +1861,7 @@
         <v>2020</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>12</v>
@@ -1879,7 +1879,7 @@
         <v>2019</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -1887,7 +1887,7 @@
         <v>2020</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>12</v>
@@ -1905,7 +1905,7 @@
         <v>2019</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -1913,7 +1913,7 @@
         <v>2020</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>12</v>
@@ -1931,7 +1931,7 @@
         <v>2019</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -1939,7 +1939,7 @@
         <v>2020</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>12</v>
@@ -1957,7 +1957,7 @@
         <v>2019</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -1965,7 +1965,7 @@
         <v>2020</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>12</v>
@@ -1983,7 +1983,7 @@
         <v>2019</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -1991,7 +1991,7 @@
         <v>2020</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>12</v>
@@ -2009,7 +2009,7 @@
         <v>2019</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2017,7 +2017,7 @@
         <v>2020</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>12</v>
@@ -2035,7 +2035,7 @@
         <v>2019</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2043,7 +2043,7 @@
         <v>2020</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>12</v>
@@ -2061,7 +2061,7 @@
         <v>2019</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2069,7 +2069,7 @@
         <v>2020</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>12</v>
@@ -2087,7 +2087,7 @@
         <v>2019</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -2095,7 +2095,7 @@
         <v>2020</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>12</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -2121,7 +2121,7 @@
         <v>2020</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>12</v>
@@ -2139,7 +2139,7 @@
         <v>2019</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -2147,7 +2147,7 @@
         <v>2020</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>12</v>
@@ -2165,7 +2165,7 @@
         <v>2019</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2173,7 +2173,7 @@
         <v>2020</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>12</v>
@@ -2191,7 +2191,7 @@
         <v>2019</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -2199,7 +2199,7 @@
         <v>2020</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>12</v>
@@ -2217,7 +2217,7 @@
         <v>2019</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2225,7 +2225,7 @@
         <v>2020</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>12</v>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2251,7 +2251,7 @@
         <v>2020</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>13</v>
@@ -2269,7 +2269,7 @@
         <v>2019</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -2277,7 +2277,7 @@
         <v>2020</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>13</v>
@@ -2295,7 +2295,7 @@
         <v>2019</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2303,7 +2303,7 @@
         <v>2020</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>13</v>
@@ -2321,7 +2321,7 @@
         <v>2019</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2329,7 +2329,7 @@
         <v>2020</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>13</v>
@@ -2347,7 +2347,7 @@
         <v>2019</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -2355,7 +2355,7 @@
         <v>2020</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>13</v>
@@ -2373,7 +2373,7 @@
         <v>2019</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -2381,7 +2381,7 @@
         <v>2020</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>13</v>
@@ -2399,7 +2399,7 @@
         <v>2019</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -2407,7 +2407,7 @@
         <v>2020</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>13</v>
@@ -2425,7 +2425,7 @@
         <v>2019</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -2433,7 +2433,7 @@
         <v>2020</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>13</v>
@@ -2451,7 +2451,7 @@
         <v>2019</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -2459,7 +2459,7 @@
         <v>2020</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>13</v>
@@ -2477,7 +2477,7 @@
         <v>2019</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -2485,7 +2485,7 @@
         <v>2020</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>13</v>
@@ -2503,7 +2503,7 @@
         <v>2019</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -2511,7 +2511,7 @@
         <v>2020</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>13</v>
@@ -2529,7 +2529,7 @@
         <v>2019</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -2537,7 +2537,7 @@
         <v>2020</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>13</v>
@@ -2555,7 +2555,7 @@
         <v>2019</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -2563,7 +2563,7 @@
         <v>2020</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>13</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -2589,7 +2589,7 @@
         <v>2020</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>13</v>
@@ -2607,7 +2607,7 @@
         <v>2019</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -2615,7 +2615,7 @@
         <v>2020</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>13</v>
@@ -2633,7 +2633,7 @@
         <v>2019</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -2641,7 +2641,7 @@
         <v>2020</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>13</v>
@@ -2659,7 +2659,7 @@
         <v>2019</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -2667,7 +2667,7 @@
         <v>2020</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>13</v>
@@ -2685,7 +2685,7 @@
         <v>2019</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -2693,7 +2693,7 @@
         <v>2020</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>13</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -2719,7 +2719,7 @@
         <v>2020</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>14</v>
@@ -2737,7 +2737,7 @@
         <v>2019</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -2745,7 +2745,7 @@
         <v>2020</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>14</v>
@@ -2763,7 +2763,7 @@
         <v>2019</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -2771,7 +2771,7 @@
         <v>2020</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>14</v>
@@ -2789,7 +2789,7 @@
         <v>2019</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -2797,7 +2797,7 @@
         <v>2020</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>14</v>
@@ -2815,7 +2815,7 @@
         <v>2019</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -2823,7 +2823,7 @@
         <v>2020</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>14</v>
@@ -2841,7 +2841,7 @@
         <v>2019</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -2849,7 +2849,7 @@
         <v>2020</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>14</v>
@@ -2867,7 +2867,7 @@
         <v>2019</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -2875,7 +2875,7 @@
         <v>2020</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>14</v>
@@ -2893,7 +2893,7 @@
         <v>2019</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -2901,7 +2901,7 @@
         <v>2020</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>14</v>
@@ -2919,7 +2919,7 @@
         <v>2019</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -2927,7 +2927,7 @@
         <v>2020</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>14</v>
@@ -2945,7 +2945,7 @@
         <v>2019</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -2953,7 +2953,7 @@
         <v>2020</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>14</v>
@@ -2971,7 +2971,7 @@
         <v>2019</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -2979,7 +2979,7 @@
         <v>2020</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>14</v>
@@ -2997,7 +2997,7 @@
         <v>2019</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -3005,7 +3005,7 @@
         <v>2020</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>14</v>
@@ -3023,7 +3023,7 @@
         <v>2019</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -3031,7 +3031,7 @@
         <v>2020</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>14</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -3057,7 +3057,7 @@
         <v>2020</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>14</v>
@@ -3075,7 +3075,7 @@
         <v>2019</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -3083,7 +3083,7 @@
         <v>2020</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>14</v>
@@ -3101,7 +3101,7 @@
         <v>2019</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -3109,7 +3109,7 @@
         <v>2020</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>14</v>
@@ -3127,7 +3127,7 @@
         <v>2019</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -3135,7 +3135,7 @@
         <v>2020</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>14</v>
@@ -3153,7 +3153,7 @@
         <v>2019</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -3161,7 +3161,7 @@
         <v>2020</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>14</v>
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -3187,7 +3187,7 @@
         <v>2020</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>15</v>
@@ -3205,7 +3205,7 @@
         <v>2019</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -3213,7 +3213,7 @@
         <v>2020</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>15</v>
@@ -3231,7 +3231,7 @@
         <v>2019</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -3239,7 +3239,7 @@
         <v>2020</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>15</v>
@@ -3257,7 +3257,7 @@
         <v>2019</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -3265,7 +3265,7 @@
         <v>2020</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>15</v>
@@ -3283,7 +3283,7 @@
         <v>2019</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -3291,7 +3291,7 @@
         <v>2020</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>15</v>
@@ -3309,7 +3309,7 @@
         <v>2019</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -3317,7 +3317,7 @@
         <v>2020</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>15</v>
@@ -3335,7 +3335,7 @@
         <v>2019</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -3343,7 +3343,7 @@
         <v>2020</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>15</v>
@@ -3361,7 +3361,7 @@
         <v>2019</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -3369,7 +3369,7 @@
         <v>2020</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>15</v>
@@ -3387,7 +3387,7 @@
         <v>2019</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -3395,7 +3395,7 @@
         <v>2020</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>15</v>
@@ -3413,7 +3413,7 @@
         <v>2019</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -3421,7 +3421,7 @@
         <v>2020</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>15</v>
@@ -3439,7 +3439,7 @@
         <v>2019</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -3447,7 +3447,7 @@
         <v>2020</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>15</v>
@@ -3465,7 +3465,7 @@
         <v>2019</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
@@ -3473,7 +3473,7 @@
         <v>2020</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>15</v>
@@ -3491,7 +3491,7 @@
         <v>2019</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -3499,7 +3499,7 @@
         <v>2020</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>15</v>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -3525,7 +3525,7 @@
         <v>2020</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>15</v>
@@ -3543,7 +3543,7 @@
         <v>2019</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -3551,7 +3551,7 @@
         <v>2020</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>15</v>
@@ -3569,7 +3569,7 @@
         <v>2019</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -3577,7 +3577,7 @@
         <v>2020</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>15</v>
@@ -3595,7 +3595,7 @@
         <v>2019</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -3603,7 +3603,7 @@
         <v>2020</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>15</v>
@@ -3621,7 +3621,7 @@
         <v>2019</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -3629,7 +3629,7 @@
         <v>2020</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>15</v>
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -3655,7 +3655,7 @@
         <v>2020</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>16</v>
@@ -3673,7 +3673,7 @@
         <v>2019</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -3681,7 +3681,7 @@
         <v>2020</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>16</v>
@@ -3699,7 +3699,7 @@
         <v>2019</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -3707,7 +3707,7 @@
         <v>2020</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>16</v>
@@ -3725,7 +3725,7 @@
         <v>2019</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -3733,7 +3733,7 @@
         <v>2020</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>16</v>
@@ -3751,7 +3751,7 @@
         <v>2019</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -3759,7 +3759,7 @@
         <v>2020</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>16</v>
@@ -3777,7 +3777,7 @@
         <v>2019</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -3785,7 +3785,7 @@
         <v>2020</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>16</v>
@@ -3803,7 +3803,7 @@
         <v>2019</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -3811,7 +3811,7 @@
         <v>2020</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>16</v>
@@ -3829,7 +3829,7 @@
         <v>2019</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -3837,7 +3837,7 @@
         <v>2020</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>16</v>
@@ -3855,7 +3855,7 @@
         <v>2019</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -3863,7 +3863,7 @@
         <v>2020</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>16</v>
@@ -3881,7 +3881,7 @@
         <v>2019</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -3889,7 +3889,7 @@
         <v>2020</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>16</v>
@@ -3907,7 +3907,7 @@
         <v>2019</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -3915,7 +3915,7 @@
         <v>2020</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>16</v>
@@ -3933,7 +3933,7 @@
         <v>2019</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -3941,7 +3941,7 @@
         <v>2020</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>16</v>
@@ -3959,7 +3959,7 @@
         <v>2019</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -3967,7 +3967,7 @@
         <v>2020</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>16</v>
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -3993,7 +3993,7 @@
         <v>2020</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>16</v>
@@ -4011,7 +4011,7 @@
         <v>2019</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -4019,7 +4019,7 @@
         <v>2020</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>16</v>
@@ -4037,7 +4037,7 @@
         <v>2019</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>2020</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>16</v>
@@ -4063,7 +4063,7 @@
         <v>2019</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -4071,7 +4071,7 @@
         <v>2020</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>16</v>
@@ -4089,7 +4089,7 @@
         <v>2019</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -4097,7 +4097,7 @@
         <v>2020</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>16</v>
@@ -4115,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
@@ -4123,7 +4123,7 @@
         <v>2020</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>12</v>
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
@@ -4149,7 +4149,7 @@
         <v>2020</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>17</v>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
@@ -4175,7 +4175,7 @@
         <v>2020</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>12</v>
@@ -4193,7 +4193,7 @@
         <v>2019</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
@@ -4201,7 +4201,7 @@
         <v>2020</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>12</v>
@@ -4219,7 +4219,7 @@
         <v>2019</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
@@ -4227,7 +4227,7 @@
         <v>2020</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>12</v>
@@ -4245,7 +4245,7 @@
         <v>2019</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -4253,7 +4253,7 @@
         <v>2020</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>12</v>
@@ -4271,7 +4271,7 @@
         <v>2019</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -4279,7 +4279,7 @@
         <v>2020</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>12</v>
@@ -4297,7 +4297,7 @@
         <v>2019</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -4305,7 +4305,7 @@
         <v>2020</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>12</v>
@@ -4323,7 +4323,7 @@
         <v>2019</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -4331,7 +4331,7 @@
         <v>2020</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>12</v>
@@ -4349,7 +4349,7 @@
         <v>2019</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
@@ -4357,7 +4357,7 @@
         <v>2020</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>12</v>
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
@@ -4383,7 +4383,7 @@
         <v>2020</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>18</v>
@@ -4401,7 +4401,7 @@
         <v>2019</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
@@ -4409,7 +4409,7 @@
         <v>2020</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>18</v>
@@ -4427,7 +4427,7 @@
         <v>2019</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -4435,7 +4435,7 @@
         <v>2020</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>18</v>
@@ -4453,7 +4453,7 @@
         <v>2019</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
@@ -4461,7 +4461,7 @@
         <v>2020</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>18</v>
@@ -4479,7 +4479,7 @@
         <v>2019</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
@@ -4487,7 +4487,7 @@
         <v>2020</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>18</v>
@@ -4505,7 +4505,7 @@
         <v>2019</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -4513,7 +4513,7 @@
         <v>2020</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>18</v>
@@ -4531,7 +4531,7 @@
         <v>2019</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -4539,7 +4539,7 @@
         <v>2020</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>18</v>
@@ -4557,7 +4557,7 @@
         <v>2019</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -4565,7 +4565,7 @@
         <v>2020</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>18</v>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -4591,7 +4591,7 @@
         <v>2020</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>19</v>
@@ -4609,7 +4609,7 @@
         <v>2019</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -4617,7 +4617,7 @@
         <v>2020</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>19</v>
@@ -4635,7 +4635,7 @@
         <v>2019</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -4643,7 +4643,7 @@
         <v>2020</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>19</v>
@@ -4661,7 +4661,7 @@
         <v>2019</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -4669,7 +4669,7 @@
         <v>2020</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>19</v>
@@ -4687,7 +4687,7 @@
         <v>2019</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -4695,7 +4695,7 @@
         <v>2020</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>19</v>
@@ -4713,7 +4713,7 @@
         <v>2019</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
@@ -4721,7 +4721,7 @@
         <v>2020</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>19</v>
@@ -4739,7 +4739,7 @@
         <v>2019</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -4747,7 +4747,7 @@
         <v>2020</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>19</v>
@@ -4765,7 +4765,7 @@
         <v>2019</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
@@ -4773,7 +4773,7 @@
         <v>2020</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>19</v>
@@ -4791,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
@@ -4799,7 +4799,7 @@
         <v>2020</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>12</v>
@@ -4817,7 +4817,7 @@
         <v>2019</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -4825,7 +4825,7 @@
         <v>2020</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>12</v>
@@ -4843,7 +4843,7 @@
         <v>2019</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
@@ -4851,7 +4851,7 @@
         <v>2020</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>12</v>
@@ -4869,7 +4869,7 @@
         <v>2019</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -4877,7 +4877,7 @@
         <v>2020</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>12</v>
@@ -4895,7 +4895,7 @@
         <v>2019</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
@@ -4903,7 +4903,7 @@
         <v>2020</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>12</v>
@@ -4921,7 +4921,7 @@
         <v>2019</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
@@ -4929,7 +4929,7 @@
         <v>2020</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>12</v>
@@ -4947,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
@@ -4955,7 +4955,7 @@
         <v>2020</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>18</v>
@@ -4973,7 +4973,7 @@
         <v>2019</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
@@ -4981,7 +4981,7 @@
         <v>2020</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>18</v>
@@ -4999,7 +4999,7 @@
         <v>2019</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
@@ -5007,7 +5007,7 @@
         <v>2020</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>18</v>
@@ -5025,7 +5025,7 @@
         <v>2019</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
@@ -5033,7 +5033,7 @@
         <v>2020</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>18</v>
@@ -5051,7 +5051,7 @@
         <v>2019</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
@@ -5059,7 +5059,7 @@
         <v>2020</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>18</v>
@@ -5077,7 +5077,7 @@
         <v>2019</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -5085,7 +5085,7 @@
         <v>2020</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>18</v>
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -5111,7 +5111,7 @@
         <v>2020</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>19</v>
@@ -5129,7 +5129,7 @@
         <v>2019</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
@@ -5137,7 +5137,7 @@
         <v>2020</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>19</v>
@@ -5155,7 +5155,7 @@
         <v>2019</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
@@ -5163,7 +5163,7 @@
         <v>2020</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>19</v>
@@ -5181,7 +5181,7 @@
         <v>2019</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
@@ -5189,7 +5189,7 @@
         <v>2020</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>19</v>
@@ -5207,7 +5207,7 @@
         <v>2019</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
@@ -5215,7 +5215,7 @@
         <v>2020</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>19</v>
@@ -5233,7 +5233,7 @@
         <v>2019</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
@@ -5241,7 +5241,7 @@
         <v>2020</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>19</v>
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
@@ -5267,7 +5267,7 @@
         <v>2020</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>18</v>
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -5293,7 +5293,7 @@
         <v>2020</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>19</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -5319,7 +5319,7 @@
         <v>2020</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>20</v>
@@ -5337,7 +5337,7 @@
         <v>2020</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
@@ -5345,7 +5345,7 @@
         <v>2020</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>20</v>
@@ -5363,7 +5363,7 @@
         <v>2020</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
@@ -5371,7 +5371,7 @@
         <v>2020</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>20</v>
@@ -5389,7 +5389,7 @@
         <v>2020</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
@@ -5397,7 +5397,7 @@
         <v>2020</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>20</v>
@@ -5415,7 +5415,7 @@
         <v>2020</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
@@ -5423,7 +5423,7 @@
         <v>2020</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>20</v>
@@ -5441,7 +5441,7 @@
         <v>2020</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -5449,7 +5449,7 @@
         <v>2020</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>20</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -5475,7 +5475,7 @@
         <v>2020</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>21</v>
@@ -5493,7 +5493,7 @@
         <v>2020</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
@@ -5501,7 +5501,7 @@
         <v>2020</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>21</v>
@@ -5519,7 +5519,7 @@
         <v>2020</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
@@ -5527,7 +5527,7 @@
         <v>2020</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>21</v>
@@ -5545,7 +5545,7 @@
         <v>2020</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
@@ -5553,7 +5553,7 @@
         <v>2020</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>21</v>
@@ -5571,7 +5571,7 @@
         <v>2020</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
@@ -5579,7 +5579,7 @@
         <v>2020</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>21</v>
@@ -5597,7 +5597,7 @@
         <v>2020</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -5605,7 +5605,7 @@
         <v>2020</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>21</v>
@@ -5623,7 +5623,7 @@
         <v>0</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
@@ -5631,7 +5631,7 @@
         <v>2020</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>22</v>
@@ -5649,7 +5649,7 @@
         <v>2020</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
@@ -5657,7 +5657,7 @@
         <v>2020</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>22</v>
@@ -5675,7 +5675,7 @@
         <v>2020</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -5683,7 +5683,7 @@
         <v>2020</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>22</v>
@@ -5701,7 +5701,7 @@
         <v>2020</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
@@ -5709,7 +5709,7 @@
         <v>2020</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>22</v>
@@ -5727,7 +5727,7 @@
         <v>2020</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
@@ -5735,7 +5735,7 @@
         <v>2020</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>22</v>
@@ -5753,7 +5753,7 @@
         <v>2020</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
@@ -5761,7 +5761,7 @@
         <v>2020</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>22</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -5787,7 +5787,7 @@
         <v>2020</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>23</v>
@@ -5805,7 +5805,7 @@
         <v>2020</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -5813,7 +5813,7 @@
         <v>2020</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>23</v>
@@ -5831,7 +5831,7 @@
         <v>2020</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
@@ -5839,7 +5839,7 @@
         <v>2020</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>23</v>
@@ -5857,7 +5857,7 @@
         <v>2020</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
@@ -5865,7 +5865,7 @@
         <v>2020</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>23</v>
@@ -5883,7 +5883,7 @@
         <v>2020</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -5891,7 +5891,7 @@
         <v>2020</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>23</v>
@@ -5909,7 +5909,7 @@
         <v>2020</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
@@ -5917,7 +5917,7 @@
         <v>2020</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>23</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
@@ -5943,7 +5943,7 @@
         <v>2020</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>24</v>
@@ -5961,7 +5961,7 @@
         <v>2020</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -5969,7 +5969,7 @@
         <v>2020</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>24</v>
@@ -5987,7 +5987,7 @@
         <v>2020</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
@@ -5995,7 +5995,7 @@
         <v>2020</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>24</v>
@@ -6013,7 +6013,7 @@
         <v>2020</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
@@ -6021,7 +6021,7 @@
         <v>2020</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>24</v>
@@ -6039,7 +6039,7 @@
         <v>2020</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -6047,7 +6047,7 @@
         <v>2020</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>24</v>
@@ -6065,7 +6065,7 @@
         <v>2020</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
@@ -6073,7 +6073,7 @@
         <v>2020</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>24</v>
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
@@ -6099,7 +6099,7 @@
         <v>2020</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>25</v>
@@ -6117,7 +6117,7 @@
         <v>2020</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -6125,7 +6125,7 @@
         <v>2020</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>25</v>
@@ -6143,7 +6143,7 @@
         <v>2020</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -6151,7 +6151,7 @@
         <v>2020</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>25</v>
@@ -6169,7 +6169,7 @@
         <v>2020</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -6177,7 +6177,7 @@
         <v>2020</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>25</v>
@@ -6195,7 +6195,7 @@
         <v>2020</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -6203,7 +6203,7 @@
         <v>2020</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>25</v>
@@ -6221,7 +6221,7 @@
         <v>2020</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -6229,7 +6229,7 @@
         <v>2020</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>25</v>
@@ -6247,7 +6247,7 @@
         <v>0</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -6255,7 +6255,7 @@
         <v>2020</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>26</v>
@@ -6273,7 +6273,7 @@
         <v>2020</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
@@ -6281,7 +6281,7 @@
         <v>2020</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>26</v>
@@ -6299,7 +6299,7 @@
         <v>2020</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -6307,7 +6307,7 @@
         <v>2020</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>26</v>
@@ -6325,7 +6325,7 @@
         <v>2020</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -6333,7 +6333,7 @@
         <v>2020</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>26</v>
@@ -6351,7 +6351,7 @@
         <v>2020</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
@@ -6359,7 +6359,7 @@
         <v>2020</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>26</v>
@@ -6377,7 +6377,7 @@
         <v>2020</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
@@ -6385,7 +6385,7 @@
         <v>2020</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>26</v>
@@ -6403,7 +6403,7 @@
         <v>0</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
@@ -6411,7 +6411,7 @@
         <v>2020</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>27</v>
@@ -6429,7 +6429,7 @@
         <v>2020</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -6437,7 +6437,7 @@
         <v>2020</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>27</v>
@@ -6455,7 +6455,7 @@
         <v>2020</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -6463,7 +6463,7 @@
         <v>2020</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>27</v>
@@ -6481,7 +6481,7 @@
         <v>2020</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
@@ -6489,7 +6489,7 @@
         <v>2020</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>27</v>
@@ -6507,7 +6507,7 @@
         <v>2020</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -6515,7 +6515,7 @@
         <v>2020</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>27</v>
@@ -6533,7 +6533,7 @@
         <v>2020</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
@@ -6541,7 +6541,7 @@
         <v>2020</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>27</v>
@@ -6559,7 +6559,7 @@
         <v>2020</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
@@ -6567,7 +6567,7 @@
         <v>2020</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>27</v>
@@ -6585,7 +6585,7 @@
         <v>2020</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
@@ -6593,7 +6593,7 @@
         <v>2020</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>27</v>
@@ -6611,7 +6611,7 @@
         <v>2020</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
@@ -6619,7 +6619,7 @@
         <v>2020</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>27</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
@@ -6645,7 +6645,7 @@
         <v>2020</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>15</v>
@@ -6663,7 +6663,7 @@
         <v>2020</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
@@ -6671,7 +6671,7 @@
         <v>2020</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>15</v>
@@ -6689,7 +6689,7 @@
         <v>2020</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
@@ -6697,7 +6697,7 @@
         <v>2020</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>15</v>
@@ -6715,7 +6715,7 @@
         <v>2020</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
@@ -6723,7 +6723,7 @@
         <v>2020</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>15</v>
@@ -6741,7 +6741,7 @@
         <v>2020</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -6749,7 +6749,7 @@
         <v>2020</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>15</v>
@@ -6767,7 +6767,7 @@
         <v>2020</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
@@ -6775,7 +6775,7 @@
         <v>2020</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>15</v>
@@ -6793,7 +6793,7 @@
         <v>2020</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
@@ -6801,7 +6801,7 @@
         <v>2020</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>15</v>
@@ -6819,7 +6819,7 @@
         <v>2020</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
@@ -6827,7 +6827,7 @@
         <v>2020</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>15</v>
@@ -6845,7 +6845,7 @@
         <v>2020</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
@@ -6853,7 +6853,7 @@
         <v>2020</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>15</v>
@@ -6871,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
@@ -6879,7 +6879,7 @@
         <v>2020</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>12</v>
@@ -6897,7 +6897,7 @@
         <v>2020</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
@@ -6905,7 +6905,7 @@
         <v>2020</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>12</v>
@@ -6923,7 +6923,7 @@
         <v>2020</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
@@ -6931,7 +6931,7 @@
         <v>2020</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>12</v>
@@ -6949,7 +6949,7 @@
         <v>2020</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
@@ -6957,7 +6957,7 @@
         <v>2020</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>12</v>
@@ -6975,7 +6975,7 @@
         <v>2020</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
@@ -6983,7 +6983,7 @@
         <v>2020</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>12</v>
@@ -7001,7 +7001,7 @@
         <v>2020</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
@@ -7009,7 +7009,7 @@
         <v>2020</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>12</v>
@@ -7027,7 +7027,7 @@
         <v>2020</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
@@ -7035,7 +7035,7 @@
         <v>2020</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>12</v>
@@ -7053,7 +7053,7 @@
         <v>2020</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
@@ -7061,7 +7061,7 @@
         <v>2020</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>12</v>
@@ -7079,7 +7079,7 @@
         <v>2020</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
@@ -7087,7 +7087,7 @@
         <v>2020</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>12</v>
@@ -7105,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
@@ -7113,7 +7113,7 @@
         <v>2020</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>23</v>
@@ -7131,7 +7131,7 @@
         <v>2020</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
@@ -7139,7 +7139,7 @@
         <v>2020</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>23</v>
@@ -7157,7 +7157,7 @@
         <v>2020</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
@@ -7165,7 +7165,7 @@
         <v>2020</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>23</v>
@@ -7183,7 +7183,7 @@
         <v>2020</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
@@ -7191,7 +7191,7 @@
         <v>2020</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>23</v>
@@ -7209,7 +7209,7 @@
         <v>2020</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
@@ -7217,7 +7217,7 @@
         <v>2020</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>23</v>
@@ -7235,7 +7235,7 @@
         <v>2020</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
@@ -7243,7 +7243,7 @@
         <v>2020</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>23</v>
@@ -7261,7 +7261,7 @@
         <v>2020</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
@@ -7269,7 +7269,7 @@
         <v>2020</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>23</v>
@@ -7287,7 +7287,7 @@
         <v>2020</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
@@ -7295,7 +7295,7 @@
         <v>2020</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>23</v>
@@ -7313,7 +7313,7 @@
         <v>2020</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
@@ -7321,7 +7321,7 @@
         <v>2020</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>23</v>
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
@@ -7347,7 +7347,7 @@
         <v>2020</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>28</v>
@@ -7365,7 +7365,7 @@
         <v>2020</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
@@ -7373,7 +7373,7 @@
         <v>2020</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>28</v>
@@ -7391,7 +7391,7 @@
         <v>2020</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
@@ -7399,7 +7399,7 @@
         <v>2020</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>28</v>
@@ -7417,7 +7417,7 @@
         <v>2020</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -7425,7 +7425,7 @@
         <v>2020</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>28</v>
@@ -7443,7 +7443,7 @@
         <v>2020</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
@@ -7451,7 +7451,7 @@
         <v>2020</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>28</v>
@@ -7469,7 +7469,7 @@
         <v>2020</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
@@ -7477,7 +7477,7 @@
         <v>2020</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>28</v>
@@ -7495,7 +7495,7 @@
         <v>2020</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
@@ -7503,7 +7503,7 @@
         <v>2020</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>28</v>
@@ -7521,7 +7521,7 @@
         <v>2020</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
@@ -7529,7 +7529,7 @@
         <v>2020</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>28</v>
@@ -7547,7 +7547,7 @@
         <v>2020</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
@@ -7555,7 +7555,7 @@
         <v>2020</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>28</v>
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
@@ -7581,7 +7581,7 @@
         <v>2020</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>27</v>
@@ -7599,7 +7599,7 @@
         <v>2020</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
@@ -7607,7 +7607,7 @@
         <v>2020</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>27</v>
@@ -7625,7 +7625,7 @@
         <v>2020</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
@@ -7633,7 +7633,7 @@
         <v>2020</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>27</v>
@@ -7651,7 +7651,7 @@
         <v>2020</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
@@ -7659,7 +7659,7 @@
         <v>2020</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>27</v>
@@ -7677,7 +7677,7 @@
         <v>2020</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
@@ -7685,7 +7685,7 @@
         <v>2020</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>27</v>
@@ -7703,7 +7703,7 @@
         <v>0</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
@@ -7711,7 +7711,7 @@
         <v>2020</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>27</v>
@@ -7729,7 +7729,7 @@
         <v>2020</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
@@ -7737,7 +7737,7 @@
         <v>2020</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>27</v>
@@ -7755,7 +7755,7 @@
         <v>2020</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
@@ -7763,7 +7763,7 @@
         <v>2020</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>27</v>
@@ -7781,7 +7781,7 @@
         <v>2020</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
@@ -7789,7 +7789,7 @@
         <v>2020</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>27</v>
@@ -7807,7 +7807,7 @@
         <v>2020</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
@@ -7815,7 +7815,7 @@
         <v>2020</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>27</v>
@@ -7833,7 +7833,7 @@
         <v>2020</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
@@ -7841,7 +7841,7 @@
         <v>2020</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>27</v>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
@@ -7867,7 +7867,7 @@
         <v>2020</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>15</v>
@@ -7885,7 +7885,7 @@
         <v>2020</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
@@ -7893,7 +7893,7 @@
         <v>2020</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>15</v>
@@ -7911,7 +7911,7 @@
         <v>2020</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
@@ -7919,7 +7919,7 @@
         <v>2020</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>15</v>
@@ -7937,7 +7937,7 @@
         <v>2020</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
@@ -7945,7 +7945,7 @@
         <v>2020</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>15</v>
@@ -7963,7 +7963,7 @@
         <v>2020</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
@@ -7971,7 +7971,7 @@
         <v>2020</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>15</v>
@@ -7989,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
@@ -7997,7 +7997,7 @@
         <v>2020</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>15</v>
@@ -8015,7 +8015,7 @@
         <v>2020</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
@@ -8023,7 +8023,7 @@
         <v>2020</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>15</v>
@@ -8041,7 +8041,7 @@
         <v>2020</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
@@ -8049,7 +8049,7 @@
         <v>2020</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>15</v>
@@ -8067,7 +8067,7 @@
         <v>2020</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
@@ -8075,7 +8075,7 @@
         <v>2020</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>15</v>
@@ -8093,7 +8093,7 @@
         <v>2020</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
@@ -8101,7 +8101,7 @@
         <v>2020</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
         <v>2020</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
@@ -8127,7 +8127,7 @@
         <v>2020</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>15</v>
@@ -8145,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
@@ -8153,7 +8153,7 @@
         <v>2020</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>12</v>
@@ -8171,7 +8171,7 @@
         <v>2020</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
@@ -8179,7 +8179,7 @@
         <v>2020</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>12</v>
@@ -8197,7 +8197,7 @@
         <v>2020</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
@@ -8205,7 +8205,7 @@
         <v>2020</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>12</v>
@@ -8223,7 +8223,7 @@
         <v>2020</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
@@ -8231,7 +8231,7 @@
         <v>2020</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>12</v>
@@ -8249,7 +8249,7 @@
         <v>2020</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
@@ -8257,7 +8257,7 @@
         <v>2020</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>12</v>
@@ -8275,7 +8275,7 @@
         <v>0</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
@@ -8283,7 +8283,7 @@
         <v>2020</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>12</v>
@@ -8301,7 +8301,7 @@
         <v>2020</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
@@ -8309,7 +8309,7 @@
         <v>2020</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>12</v>
@@ -8327,7 +8327,7 @@
         <v>2020</v>
       </c>
       <c r="I294" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
@@ -8335,7 +8335,7 @@
         <v>2020</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>12</v>
@@ -8353,7 +8353,7 @@
         <v>2020</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
@@ -8361,7 +8361,7 @@
         <v>2020</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>12</v>
@@ -8379,7 +8379,7 @@
         <v>2020</v>
       </c>
       <c r="I296" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
@@ -8387,7 +8387,7 @@
         <v>2020</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>12</v>
@@ -8405,7 +8405,7 @@
         <v>2020</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
         <v>2020</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>12</v>
@@ -8431,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
@@ -8439,7 +8439,7 @@
         <v>2020</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>23</v>
@@ -8457,7 +8457,7 @@
         <v>2020</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
@@ -8465,7 +8465,7 @@
         <v>2020</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>23</v>
@@ -8483,7 +8483,7 @@
         <v>2020</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
@@ -8491,7 +8491,7 @@
         <v>2020</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>23</v>
@@ -8509,7 +8509,7 @@
         <v>2020</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
@@ -8517,7 +8517,7 @@
         <v>2020</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>23</v>
@@ -8535,7 +8535,7 @@
         <v>2020</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
@@ -8543,7 +8543,7 @@
         <v>2020</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>23</v>
@@ -8561,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
@@ -8569,7 +8569,7 @@
         <v>2020</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>23</v>
@@ -8587,7 +8587,7 @@
         <v>2020</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.25">
@@ -8595,7 +8595,7 @@
         <v>2020</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>23</v>
@@ -8613,7 +8613,7 @@
         <v>2020</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.25">
@@ -8621,7 +8621,7 @@
         <v>2020</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>23</v>
@@ -8639,7 +8639,7 @@
         <v>2020</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
@@ -8647,7 +8647,7 @@
         <v>2020</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>23</v>
@@ -8665,7 +8665,7 @@
         <v>2020</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
@@ -8673,7 +8673,7 @@
         <v>2020</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>23</v>
@@ -8691,7 +8691,7 @@
         <v>2020</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
@@ -8699,7 +8699,7 @@
         <v>2020</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>23</v>
@@ -8717,7 +8717,7 @@
         <v>0</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
@@ -8725,7 +8725,7 @@
         <v>2020</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>28</v>
@@ -8743,7 +8743,7 @@
         <v>2020</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
@@ -8751,7 +8751,7 @@
         <v>2020</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>28</v>
@@ -8769,7 +8769,7 @@
         <v>2020</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
@@ -8777,7 +8777,7 @@
         <v>2020</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>2020</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
@@ -8803,7 +8803,7 @@
         <v>2020</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>28</v>
@@ -8821,7 +8821,7 @@
         <v>2020</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.25">
@@ -8829,7 +8829,7 @@
         <v>2020</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>28</v>
@@ -8847,7 +8847,7 @@
         <v>0</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.25">
@@ -8855,7 +8855,7 @@
         <v>2020</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>28</v>
@@ -8873,7 +8873,7 @@
         <v>2020</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
@@ -8881,7 +8881,7 @@
         <v>2020</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>28</v>
@@ -8899,7 +8899,7 @@
         <v>2020</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
@@ -8907,7 +8907,7 @@
         <v>2020</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>28</v>
@@ -8925,7 +8925,7 @@
         <v>2020</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
@@ -8933,7 +8933,7 @@
         <v>2020</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>28</v>
@@ -8951,7 +8951,7 @@
         <v>2020</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
@@ -8959,7 +8959,7 @@
         <v>2020</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>2020</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
@@ -8985,7 +8985,7 @@
         <v>2020</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>28</v>
@@ -9003,7 +9003,7 @@
         <v>0</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
